--- a/courses/Micro-And-Macro-Economics/projects/in-progress/imperfect-competition-marginal-revenue/monsanto-seed-market-template.xlsx
+++ b/courses/Micro-And-Macro-Economics/projects/in-progress/imperfect-competition-marginal-revenue/monsanto-seed-market-template.xlsx
@@ -1,333 +1,379 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\shidler\courses\BUS-620-Micro-And-Macro-Economics\ignore\in-progess\imperfect-competition-marginal-revenue\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B929A42-7214-4985-A1CE-CB75B04484CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="NonGMO Perfect" sheetId="2" r:id="rId2"/>
-    <sheet name="GMO Monopoly" sheetId="3" r:id="rId3"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="NonGMO Perfect" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="GMO Monopoly" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="g_a">'GMO Monopoly'!$C$7</definedName>
-    <definedName name="g_b">'GMO Monopoly'!$C$8</definedName>
-    <definedName name="g_Di">'GMO Monopoly'!$C$5</definedName>
-    <definedName name="g_Ds">'GMO Monopoly'!$C$6</definedName>
-    <definedName name="g_FC">'GMO Monopoly'!$C$9</definedName>
-    <definedName name="g_Popt">'GMO Monopoly'!$C$18</definedName>
-    <definedName name="g_Qopt">'GMO Monopoly'!$C$17</definedName>
-    <definedName name="ng_a">'NonGMO Perfect'!$C$6</definedName>
-    <definedName name="ng_b">'NonGMO Perfect'!$C$7</definedName>
-    <definedName name="ng_FC">'NonGMO Perfect'!$C$8</definedName>
-    <definedName name="ng_P">'NonGMO Perfect'!$C$5</definedName>
-    <definedName name="ng_Qopt">'NonGMO Perfect'!$C$12</definedName>
+    <definedName function="false" hidden="false" name="g_a" vbProcedure="false">'GMO Monopoly'!$C$7</definedName>
+    <definedName function="false" hidden="false" name="g_b" vbProcedure="false">'GMO Monopoly'!$C$8</definedName>
+    <definedName function="false" hidden="false" name="g_Di" vbProcedure="false">'GMO Monopoly'!$C$5</definedName>
+    <definedName function="false" hidden="false" name="g_Ds" vbProcedure="false">'GMO Monopoly'!$C$6</definedName>
+    <definedName function="false" hidden="false" name="g_FC" vbProcedure="false">'GMO Monopoly'!$C$9</definedName>
+    <definedName function="false" hidden="false" name="g_Popt" vbProcedure="false">'GMO Monopoly'!$C$18</definedName>
+    <definedName function="false" hidden="false" name="g_Qopt" vbProcedure="false">'GMO Monopoly'!$C$17</definedName>
+    <definedName function="false" hidden="false" name="ng_a" vbProcedure="false">'NonGMO Perfect'!$C$6</definedName>
+    <definedName function="false" hidden="false" name="ng_b" vbProcedure="false">'NonGMO Perfect'!$C$7</definedName>
+    <definedName function="false" hidden="false" name="ng_FC" vbProcedure="false">'NonGMO Perfect'!$C$8</definedName>
+    <definedName function="false" hidden="false" name="ng_P" vbProcedure="false">'NonGMO Perfect'!$C$5</definedName>
+    <definedName function="false" hidden="false" name="ng_Qopt" vbProcedure="false">'NonGMO Perfect'!$C$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
-  <si>
-    <t>Monsanto Seed Market — Perfect vs Imperfect Competition</t>
-  </si>
-  <si>
-    <t>BUS 620 · Micro &amp; Macro Economics · Shidler College of Business</t>
-  </si>
-  <si>
-    <t>Two sheets, one company, two market structures. 'NonGMO Perfect': Monsanto sells commodity corn seed at the market price ($120/bag) — a price taker, P = MC. 'GMO Monopoly': patented Roundup Ready corn gives downward-sloping demand — now selling one more bag lowers the price on every bag, so marginal revenue falls twice as fast as demand, and the rule becomes MR = MC.</t>
-  </si>
-  <si>
-    <t>HOW TO USE</t>
-  </si>
-  <si>
-    <t>1. Blue cells are inputs; black cells are formulas. Yellow cells are the answers you compute (the instructor key has them filled).</t>
-  </si>
-  <si>
-    <t>2. Cost structure on both sheets: TVC = a·Q + b·Q², so MC = a + 2b·Q. Variable cost is the AREA UNDER the MC curve — never MC × Q. (The old v9 workbook made exactly that error and understated GMO profit by ~$1.1bn.)</t>
-  </si>
-  <si>
-    <t>3. On the GMO sheet, derive MR from demand (same intercept, twice the slope), set MR = MC for Q*, then read P* off the DEMAND curve — not off MR. Reading price off MR is the classic mistake.</t>
-  </si>
-  <si>
-    <t>4. The decision tables tabulate every quantity so you can SEE the marker row where the optimum lives; the charts plot D, MR, and MC.</t>
-  </si>
-  <si>
-    <t>5. Compare: competitive GMO benchmark (P = MC) gives Q ≈ 60.2m bags at ~$121 — almost exactly the non-GMO price. Monopoly cuts output to ~34.0m, prices at ~$297, and society loses ~$3.0bn of surplus (the DWL block).</t>
-  </si>
-  <si>
-    <t>REAL-WORLD ANCHORS (validated 2026-07; see project README.md for sources)</t>
-  </si>
-  <si>
-    <t>GMO corn seed ≈ $250–305/bag vs non-GMO ≈ $85–150 (case uses $270 vs $120; the $150 trait premium is mid-range). A bag = 80,000 kernels ≈ 2.5 acres. Monsanto traits were planted on ~80% of U.S. corn and 90%+ of soybean acres. Bayer closed its $63bn acquisition June 2018 after the largest U.S. antitrust divestiture ever (~$9bn to BASF).</t>
-  </si>
-  <si>
-    <t>MODEL NOTE</t>
-  </si>
-  <si>
-    <t>The case docx quotes MC = 0.000029·Q (non-GMO) and 0.00000196·Q (GMO). Those were regression artifacts of the old workbook's tables. This workbook defines TVC = a·Q + b·Q² directly (a = $1, b = 0.000015 and 0.000001) so MC, totals, and optima are exactly self-consistent.</t>
-  </si>
-  <si>
-    <t>Non-GMO corn seed — perfect competition (price taker)</t>
-  </si>
-  <si>
-    <t>ASSUMPTIONS</t>
-  </si>
-  <si>
-    <t>Market price P ($/bag)</t>
-  </si>
-  <si>
-    <t>flat demand: the market sets it</t>
-  </si>
-  <si>
-    <t>MC intercept a ($/bag)</t>
-  </si>
-  <si>
-    <t>TVC = a·Q + b·Q²  →  MC = a + 2b·Q</t>
-  </si>
-  <si>
-    <t>MC curvature b</t>
-  </si>
-  <si>
-    <t>diminishing returns in seed production</t>
-  </si>
-  <si>
-    <t>Fixed costs ($)</t>
-  </si>
-  <si>
-    <t>seeds business overhead</t>
-  </si>
-  <si>
-    <t>Real-world anchor</t>
-  </si>
-  <si>
-    <t>≈10m non-GMO acres ÷ 2.5 acres/bag ≈ 4.0m bags</t>
-  </si>
-  <si>
-    <t>OPTIMAL — a price taker produces until P = MC</t>
-  </si>
-  <si>
-    <t>Optimal output Q* (bags)</t>
-  </si>
-  <si>
-    <t>← set P = MC and solve: Q* = (P − a) / 2b</t>
-  </si>
-  <si>
-    <t>MC at Q*</t>
-  </si>
-  <si>
-    <t>should equal P</t>
-  </si>
-  <si>
-    <t>Revenue at Q*</t>
-  </si>
-  <si>
-    <t>Variable cost (area under MC)</t>
-  </si>
-  <si>
-    <t>NOT MC × Q</t>
-  </si>
-  <si>
-    <t>Total cost</t>
-  </si>
-  <si>
-    <t>Profit at Q*</t>
-  </si>
-  <si>
-    <t>short-run; entry competes this away long-run</t>
-  </si>
-  <si>
-    <t>DECISION TABLE</t>
-  </si>
-  <si>
-    <t>Q bags</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>TVC</t>
-  </si>
-  <si>
-    <t>Profit</t>
-  </si>
-  <si>
-    <t>MR = ΔTR/ΔQ</t>
-  </si>
-  <si>
-    <t>MC = ΔTC/ΔQ</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Q mid</t>
-  </si>
-  <si>
-    <t>Roundup Ready GMO corn seed — patent monopoly (price maker)</t>
-  </si>
-  <si>
-    <t>Demand intercept ($/bag)</t>
-  </si>
-  <si>
-    <t>P = 525 − 0.0000067·Q</t>
-  </si>
-  <si>
-    <t>Demand slope ($ per bag)</t>
-  </si>
-  <si>
-    <t>each extra bag sold lowers the price a hair — on ALL bags</t>
-  </si>
-  <si>
-    <t>GMO production scales better than non-GMO (b is 15× smaller)</t>
-  </si>
-  <si>
-    <t>same seeds business overhead</t>
-  </si>
-  <si>
-    <t>≈86m GMO acres ÷ 2.5 acres/bag ≈ 34.4m bags at ≈$270</t>
-  </si>
-  <si>
-    <t>MARGINAL REVENUE — the twice-as-steep rule</t>
-  </si>
-  <si>
-    <t>MR intercept</t>
-  </si>
-  <si>
-    <t>same intercept as demand</t>
-  </si>
-  <si>
-    <t>MR slope</t>
-  </si>
-  <si>
-    <t>twice the demand slope: MR = 525 − 0.0000134·Q</t>
-  </si>
-  <si>
-    <t>OPTIMAL — a price maker produces until MR = MC</t>
-  </si>
-  <si>
-    <t>← set MR = MC: Q* = (a_D − a_MC) / (2b_MC − 2b_D)</t>
-  </si>
-  <si>
-    <t>Price P* ($/bag)</t>
-  </si>
-  <si>
-    <t>← read P* off the DEMAND curve, never off MR</t>
-  </si>
-  <si>
-    <t>MR at Q*</t>
-  </si>
-  <si>
-    <t>should equal MC at Q*</t>
-  </si>
-  <si>
-    <t>the patent moat protects this from entry</t>
-  </si>
-  <si>
-    <t>Markup P*/MC</t>
-  </si>
-  <si>
-    <t>a price taker's markup is 1.0×</t>
-  </si>
-  <si>
-    <t>Lerner index (P−MC)/P</t>
-  </si>
-  <si>
-    <t>0 = perfect competition, →1 = pure monopoly power</t>
-  </si>
-  <si>
-    <t>WHAT IF GMO SEED WERE COMPETITIVE? (P = MC benchmark)</t>
-  </si>
-  <si>
-    <t>Competitive quantity Qc</t>
-  </si>
-  <si>
-    <t>≈60.2m bags</t>
-  </si>
-  <si>
-    <t>Competitive price Pc</t>
-  </si>
-  <si>
-    <t>≈$121 — almost exactly the non-GMO price</t>
-  </si>
-  <si>
-    <t>Deadweight loss of monopoly</t>
-  </si>
-  <si>
-    <t>value destroyed, not transferred — ≈$3.0bn/yr</t>
-  </si>
-  <si>
-    <t>P (demand)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
+  <si>
+    <t xml:space="preserve">Monsanto Seed Market — Perfect vs Imperfect Competition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS 620 · Micro &amp; Macro Economics · Shidler College of Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two sheets, one company, two market structures. 'NonGMO Perfect': Monsanto sells commodity corn seed at the market price ($120/bag) — a price taker, P = MC. 'GMO Monopoly': patented Roundup Ready corn gives downward-sloping demand — now selling one more bag lowers the price on every bag, so marginal revenue falls twice as fast as demand, and the rule becomes MR = MC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOW TO USE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Blue cells are inputs; black cells are formulas. Yellow cells are the answers you compute (the instructor key has them filled).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Cost structure on both sheets: TVC = a·Q + b·Q², so MC = a + 2b·Q. Variable cost is the AREA UNDER the MC curve — never MC × Q. (The old v9 workbook made exactly that error and understated GMO profit by ~$1.1bn.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. On the GMO sheet, derive MR from demand (same intercept, twice the slope), set MR = MC for Q*, then read P* off the DEMAND curve — not off MR. Reading price off MR is the classic mistake.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. The decision tables tabulate every quantity so you can SEE the marker row where the optimum lives; the charts plot D, MR, and MC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Compare: competitive GMO benchmark (P = MC) gives Q ≈ 60.2m bags at ~$121 — almost exactly the non-GMO price. Monopoly cuts output to ~34.0m, prices at ~$297, and society loses ~$3.0bn of surplus (the DWL block).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REAL-WORLD ANCHORS (validated 2026-07; see project README.md for sources)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMO corn seed ≈ $250–305/bag vs non-GMO ≈ $85–150 (case uses $270 vs $120; the $150 trait premium is mid-range). A bag = 80,000 kernels ≈ 2.5 acres. Monsanto traits were planted on ~80% of U.S. corn and 90%+ of soybean acres. Bayer closed its $63bn acquisition June 2018 after the largest U.S. antitrust divestiture ever (~$9bn to BASF).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODEL NOTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The case docx quotes MC = 0.000029·Q (non-GMO) and 0.00000196·Q (GMO). Those were regression artifacts of the old workbook's tables. This workbook defines TVC = a·Q + b·Q² directly (a = $1, b = 0.000015 and 0.000001) so MC, totals, and optima are exactly self-consistent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR KEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue text = input you can change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black text = formula (do not overtype)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow fill = answer cells you complete (filled in the instructor key)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-GMO corn seed — perfect competition (price taker)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market price P ($/bag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flat demand: the market sets it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC intercept a ($/bag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVC = a·Q + b·Q²  →  MC = a + 2b·Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC curvature b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diminishing returns in seed production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed costs ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seeds business overhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real-world anchor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈10m non-GMO acres ÷ 2.5 acres/bag ≈ 4.0m bags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMAL — a price taker produces until P = MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimal output Q* (bags)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← set P = MC and solve: Q* = (P − a) / 2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC at Q*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">should equal P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue at Q*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable cost (area under MC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT MC × Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit at Q*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short-run; entry competes this away long-run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECISION TABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q bags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR = ΔTR/ΔQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC = ΔTC/ΔQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roundup Ready GMO corn seed — patent monopoly (price maker)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand intercept ($/bag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P = 525 − 0.0000067·Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand slope ($ per bag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">each extra bag sold lowers the price a hair — on ALL bags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMO production scales better than non-GMO (b is 15× smaller)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same seeds business overhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈86m GMO acres ÷ 2.5 acres/bag ≈ 34.4m bags at ≈$270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARGINAL REVENUE — the twice-as-steep rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR intercept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same intercept as demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">twice the demand slope: MR = 525 − 0.0000134·Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPTIMAL — a price maker produces until MR = MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← set MR = MC: Q* = (a_D − a_MC) / (2b_MC − 2b_D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price P* ($/bag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← read P* off the DEMAND curve, never off MR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR at Q*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">should equal MC at Q*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the patent moat protects this from entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markup P*/MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a price taker's markup is 1.0×</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lerner index (P−MC)/P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 = perfect competition, →1 = pure monopoly power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT IF GMO SEED WERE COMPETITIVE? (P = MC benchmark)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competitive quantity Qc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈60.2m bags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competitive price Pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈$121 — almost exactly the non-GMO price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadweight loss of monopoly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value destroyed, not transferred — ≈$3.0bn/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P (demand)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);&quot;-&quot;"/>
-    <numFmt numFmtId="165" formatCode="\$#,##0.00;\(\$#,##0.00\);&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0000000"/>
-    <numFmt numFmtId="167" formatCode="0.0&quot;×&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.0000000"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0\×"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -339,22 +385,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E5F"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF1F4E5F"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5E8F0"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -362,92 +411,299 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+  <cellXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF878787"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FFBE4B48"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFD5E8F0"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF98B855"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF4A7EBB"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF1F4E5F"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
               <a:t>Non-GMO: P vs MC</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="1"/>
+        <c:scatterStyle val="line"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>MC</c:v>
+            <c:strRef>
+              <c:f>"MC"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:solidFill>
+              <a:srgbClr val="4A7EBB"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="4A7EBB"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'NonGMO Perfect'!$K$22:$K$37</c:f>
@@ -509,7 +765,7 @@
             <c:numRef>
               <c:f>'NonGMO Perfect'!$I$22:$I$37</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;\(\$#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>8.5</c:v>
@@ -563,26 +819,74 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-37F7-4A68-85AB-F209A4B51761}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>P = MR</c:v>
+            <c:strRef>
+              <c:f>"P = MR"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>P = MR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:solidFill>
+              <a:srgbClr val="BE4B48"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="BE4B48"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'NonGMO Perfect'!$K$22:$K$37</c:f>
@@ -644,7 +948,7 @@
             <c:numRef>
               <c:f>'NonGMO Perfect'!$H$22:$H$37</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;\(\$#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>120</c:v>
@@ -698,150 +1002,332 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-37F7-4A68-85AB-F209A4B51761}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="10"/>
-        <c:axId val="20"/>
+        <c:axId val="78956804"/>
+        <c:axId val="4599517"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="10"/>
+        <c:axId val="78956804"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
                   <a:t>bags</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
         </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="20"/>
-        <c:crosses val="autoZero"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="4599517"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="20"/>
+        <c:axId val="4599517"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
                   <a:t>$/bag</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0.00;\(\$#,##0.00\);&quot;-&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="78956804"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
       <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
               <a:t>GMO: Demand, MR, MC</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="1"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="1"/>
+        <c:scatterStyle val="line"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Demand P(Q)</c:v>
+            <c:strRef>
+              <c:f>"Demand P(Q)"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Demand P(Q)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:solidFill>
+              <a:srgbClr val="4A7EBB"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="4A7EBB"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'GMO Monopoly'!$B$35:$B$59</c:f>
@@ -930,7 +1416,7 @@
             <c:numRef>
               <c:f>'GMO Monopoly'!$C$35:$C$59</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;\(\$#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
                   <c:v>525</c:v>
@@ -1011,26 +1497,74 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ACBF-4561-A830-DFF2592713EA}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>MR</c:v>
+            <c:strRef>
+              <c:f>"MR"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MR</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:solidFill>
+              <a:srgbClr val="BE4B48"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="BE4B48"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'GMO Monopoly'!$K$36:$K$59</c:f>
@@ -1116,7 +1650,7 @@
             <c:numRef>
               <c:f>'GMO Monopoly'!$H$36:$H$59</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;\(\$#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>508.25</c:v>
@@ -1194,26 +1728,74 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-ACBF-4561-A830-DFF2592713EA}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
-            <c:v>MC</c:v>
+            <c:strRef>
+              <c:f>"MC"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
+            <a:solidFill>
+              <a:srgbClr val="98B855"/>
+            </a:solidFill>
+            <a:ln w="12600">
+              <a:solidFill>
+                <a:srgbClr val="98B855"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="12600">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>'GMO Monopoly'!$K$36:$K$59</c:f>
@@ -1299,7 +1881,7 @@
             <c:numRef>
               <c:f>'GMO Monopoly'!$I$36:$I$59</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;\(\$#,##0.00\);"-"</c:formatCode>
+                <c:formatCode>\$#,##0.00;"($"#,##0.00\);\-</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>3.5</c:v>
@@ -1377,130 +1959,676 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-ACBF-4561-A830-DFF2592713EA}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="10"/>
-        <c:axId val="20"/>
+        <c:axId val="33506784"/>
+        <c:axId val="51941513"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="10"/>
+        <c:axId val="33506784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="0"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
                   <a:t>bags</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
         </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="20"/>
-        <c:crosses val="autoZero"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="51941513"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="20"/>
+        <c:axId val="51941513"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
                   <a:t>$/bag</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:overlay val="1"/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
         </c:title>
-        <c:numFmt formatCode="\$#,##0.00;\(\$#,##0.00\);&quot;-&quot;" sourceLinked="1"/>
+        <c:numFmt formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="33506784"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
       <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5400000" cy="2880000"/>
-    <xdr:graphicFrame macro="">
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>38880</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>165240</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="13956120" y="3486240"/>
+        <a:ext cx="5399640" cy="2879640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1509,34 +2637,33 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5760000" cy="3240000"/>
-    <xdr:graphicFrame macro="">
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>398880</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>163080</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="14238000" y="6019920"/>
+        <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1545,19 +2672,19 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1592,2544 +2719,2483 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:B23"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="112" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="112"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:K37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="D5" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1.5E-5</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1.5E-005</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>130000000</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="10">
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="11">
-        <f>ng_a+2*ng_b*ng_Qopt</f>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <f aca="false">ng_a+2*ng_b*ng_Qopt</f>
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="12">
-        <f>ng_P*ng_Qopt</f>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <f aca="false">ng_P*ng_Qopt</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="12">
-        <f>ng_a*ng_Qopt+ng_b*ng_Qopt^2</f>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <f aca="false">ng_a*ng_Qopt+ng_b*ng_Qopt^2</f>
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="12">
-        <f>ng_a*ng_Qopt+ng_b*ng_Qopt^2+ng_FC</f>
+      <c r="D15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <f aca="false">ng_a*ng_Qopt+ng_b*ng_Qopt^2+ng_FC</f>
         <v>130000000</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="12">
-        <f>ng_P*ng_Qopt-(ng_a*ng_Qopt+ng_b*ng_Qopt^2+ng_FC)</f>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <f aca="false">ng_P*ng_Qopt-(ng_a*ng_Qopt+ng_b*ng_Qopt^2+ng_FC)</f>
         <v>-130000000</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B20" s="13" t="s">
+      <c r="D17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K20" s="13" t="s">
+      <c r="G20" s="15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B21" s="14">
+      <c r="H20" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="12">
-        <f t="shared" ref="C21:C37" si="0">ng_P</f>
+      <c r="C21" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D21" s="12">
-        <f t="shared" ref="D21:D37" si="1">C21*B21</f>
+      <c r="D21" s="14" t="n">
+        <f aca="false">C21*B21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="12">
-        <f t="shared" ref="E21:E37" si="2">ng_a*B21+ng_b*B21^2</f>
+      <c r="E21" s="14" t="n">
+        <f aca="false">ng_a*B21+ng_b*B21^2</f>
         <v>0</v>
       </c>
-      <c r="F21" s="12">
-        <f t="shared" ref="F21:F37" si="3">E21+ng_FC</f>
+      <c r="F21" s="14" t="n">
+        <f aca="false">E21+ng_FC</f>
         <v>130000000</v>
       </c>
-      <c r="G21" s="12">
-        <f t="shared" ref="G21:G37" si="4">D21-F21</f>
+      <c r="G21" s="14" t="n">
+        <f aca="false">D21-F21</f>
         <v>-130000000</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B22" s="14">
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="16" t="n">
         <v>500000</v>
       </c>
-      <c r="C22" s="12">
-        <f t="shared" si="0"/>
+      <c r="C22" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D22" s="12">
-        <f t="shared" si="1"/>
+      <c r="D22" s="14" t="n">
+        <f aca="false">C22*B22</f>
         <v>60000000</v>
       </c>
-      <c r="E22" s="12">
-        <f t="shared" si="2"/>
+      <c r="E22" s="14" t="n">
+        <f aca="false">ng_a*B22+ng_b*B22^2</f>
         <v>4250000</v>
       </c>
-      <c r="F22" s="12">
-        <f t="shared" si="3"/>
+      <c r="F22" s="14" t="n">
+        <f aca="false">E22+ng_FC</f>
         <v>134250000</v>
       </c>
-      <c r="G22" s="12">
-        <f t="shared" si="4"/>
+      <c r="G22" s="14" t="n">
+        <f aca="false">D22-F22</f>
         <v>-74250000</v>
       </c>
-      <c r="H22" s="11">
-        <f t="shared" ref="H22:H37" si="5">(D22-D21)/(B22-B21)</f>
+      <c r="H22" s="13" t="n">
+        <f aca="false">(D22-D21)/(B22-B21)</f>
         <v>120</v>
       </c>
-      <c r="I22" s="11">
-        <f t="shared" ref="I22:I37" si="6">(F22-F21)/(B22-B21)</f>
+      <c r="I22" s="13" t="n">
+        <f aca="false">(F22-F21)/(B22-B21)</f>
         <v>8.5</v>
       </c>
-      <c r="J22" s="6" t="str">
-        <f t="shared" ref="J22:J36" si="7">IF(AND(ng_P&gt;I22,ng_P&lt;=I23),"&lt;-- P ~ MC","")</f>
+      <c r="J22" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I22,ng_P&lt;=I23),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K22" s="14">
-        <f t="shared" ref="K22:K37" si="8">(B22+B21)/2</f>
+      <c r="K22" s="16" t="n">
+        <f aca="false">(B22+B21)/2</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B23" s="14">
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="16" t="n">
         <v>1000000</v>
       </c>
-      <c r="C23" s="12">
-        <f t="shared" si="0"/>
+      <c r="C23" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D23" s="12">
-        <f t="shared" si="1"/>
+      <c r="D23" s="14" t="n">
+        <f aca="false">C23*B23</f>
         <v>120000000</v>
       </c>
-      <c r="E23" s="12">
-        <f t="shared" si="2"/>
+      <c r="E23" s="14" t="n">
+        <f aca="false">ng_a*B23+ng_b*B23^2</f>
         <v>16000000</v>
       </c>
-      <c r="F23" s="12">
-        <f t="shared" si="3"/>
+      <c r="F23" s="14" t="n">
+        <f aca="false">E23+ng_FC</f>
         <v>146000000</v>
       </c>
-      <c r="G23" s="12">
-        <f t="shared" si="4"/>
+      <c r="G23" s="14" t="n">
+        <f aca="false">D23-F23</f>
         <v>-26000000</v>
       </c>
-      <c r="H23" s="11">
-        <f t="shared" si="5"/>
+      <c r="H23" s="13" t="n">
+        <f aca="false">(D23-D22)/(B23-B22)</f>
         <v>120</v>
       </c>
-      <c r="I23" s="11">
-        <f t="shared" si="6"/>
+      <c r="I23" s="13" t="n">
+        <f aca="false">(F23-F22)/(B23-B22)</f>
         <v>23.5</v>
       </c>
-      <c r="J23" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J23" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I23,ng_P&lt;=I24),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K23" s="14">
-        <f t="shared" si="8"/>
+      <c r="K23" s="16" t="n">
+        <f aca="false">(B23+B22)/2</f>
         <v>750000</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B24" s="14">
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="16" t="n">
         <v>1500000</v>
       </c>
-      <c r="C24" s="12">
-        <f t="shared" si="0"/>
+      <c r="C24" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D24" s="12">
-        <f t="shared" si="1"/>
+      <c r="D24" s="14" t="n">
+        <f aca="false">C24*B24</f>
         <v>180000000</v>
       </c>
-      <c r="E24" s="12">
-        <f t="shared" si="2"/>
+      <c r="E24" s="14" t="n">
+        <f aca="false">ng_a*B24+ng_b*B24^2</f>
         <v>35250000</v>
       </c>
-      <c r="F24" s="12">
-        <f t="shared" si="3"/>
+      <c r="F24" s="14" t="n">
+        <f aca="false">E24+ng_FC</f>
         <v>165250000</v>
       </c>
-      <c r="G24" s="12">
-        <f t="shared" si="4"/>
+      <c r="G24" s="14" t="n">
+        <f aca="false">D24-F24</f>
         <v>14750000</v>
       </c>
-      <c r="H24" s="11">
-        <f t="shared" si="5"/>
+      <c r="H24" s="13" t="n">
+        <f aca="false">(D24-D23)/(B24-B23)</f>
         <v>120</v>
       </c>
-      <c r="I24" s="11">
-        <f t="shared" si="6"/>
+      <c r="I24" s="13" t="n">
+        <f aca="false">(F24-F23)/(B24-B23)</f>
         <v>38.5</v>
       </c>
-      <c r="J24" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J24" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I24,ng_P&lt;=I25),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K24" s="14">
-        <f t="shared" si="8"/>
+      <c r="K24" s="16" t="n">
+        <f aca="false">(B24+B23)/2</f>
         <v>1250000</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B25" s="14">
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="16" t="n">
         <v>2000000</v>
       </c>
-      <c r="C25" s="12">
-        <f t="shared" si="0"/>
+      <c r="C25" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D25" s="12">
-        <f t="shared" si="1"/>
+      <c r="D25" s="14" t="n">
+        <f aca="false">C25*B25</f>
         <v>240000000</v>
       </c>
-      <c r="E25" s="12">
-        <f t="shared" si="2"/>
+      <c r="E25" s="14" t="n">
+        <f aca="false">ng_a*B25+ng_b*B25^2</f>
         <v>62000000</v>
       </c>
-      <c r="F25" s="12">
-        <f t="shared" si="3"/>
+      <c r="F25" s="14" t="n">
+        <f aca="false">E25+ng_FC</f>
         <v>192000000</v>
       </c>
-      <c r="G25" s="12">
-        <f t="shared" si="4"/>
+      <c r="G25" s="14" t="n">
+        <f aca="false">D25-F25</f>
         <v>48000000</v>
       </c>
-      <c r="H25" s="11">
-        <f t="shared" si="5"/>
+      <c r="H25" s="13" t="n">
+        <f aca="false">(D25-D24)/(B25-B24)</f>
         <v>120</v>
       </c>
-      <c r="I25" s="11">
-        <f t="shared" si="6"/>
+      <c r="I25" s="13" t="n">
+        <f aca="false">(F25-F24)/(B25-B24)</f>
         <v>53.5</v>
       </c>
-      <c r="J25" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J25" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I25,ng_P&lt;=I26),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K25" s="14">
-        <f t="shared" si="8"/>
+      <c r="K25" s="16" t="n">
+        <f aca="false">(B25+B24)/2</f>
         <v>1750000</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B26" s="14">
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="16" t="n">
         <v>2500000</v>
       </c>
-      <c r="C26" s="12">
-        <f t="shared" si="0"/>
+      <c r="C26" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D26" s="12">
-        <f t="shared" si="1"/>
+      <c r="D26" s="14" t="n">
+        <f aca="false">C26*B26</f>
         <v>300000000</v>
       </c>
-      <c r="E26" s="12">
-        <f t="shared" si="2"/>
+      <c r="E26" s="14" t="n">
+        <f aca="false">ng_a*B26+ng_b*B26^2</f>
         <v>96250000</v>
       </c>
-      <c r="F26" s="12">
-        <f t="shared" si="3"/>
+      <c r="F26" s="14" t="n">
+        <f aca="false">E26+ng_FC</f>
         <v>226250000</v>
       </c>
-      <c r="G26" s="12">
-        <f t="shared" si="4"/>
+      <c r="G26" s="14" t="n">
+        <f aca="false">D26-F26</f>
         <v>73750000</v>
       </c>
-      <c r="H26" s="11">
-        <f t="shared" si="5"/>
+      <c r="H26" s="13" t="n">
+        <f aca="false">(D26-D25)/(B26-B25)</f>
         <v>120</v>
       </c>
-      <c r="I26" s="11">
-        <f t="shared" si="6"/>
+      <c r="I26" s="13" t="n">
+        <f aca="false">(F26-F25)/(B26-B25)</f>
         <v>68.5</v>
       </c>
-      <c r="J26" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J26" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I26,ng_P&lt;=I27),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K26" s="14">
-        <f t="shared" si="8"/>
+      <c r="K26" s="16" t="n">
+        <f aca="false">(B26+B25)/2</f>
         <v>2250000</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B27" s="14">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="16" t="n">
         <v>3000000</v>
       </c>
-      <c r="C27" s="12">
-        <f t="shared" si="0"/>
+      <c r="C27" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D27" s="12">
-        <f t="shared" si="1"/>
+      <c r="D27" s="14" t="n">
+        <f aca="false">C27*B27</f>
         <v>360000000</v>
       </c>
-      <c r="E27" s="12">
-        <f t="shared" si="2"/>
+      <c r="E27" s="14" t="n">
+        <f aca="false">ng_a*B27+ng_b*B27^2</f>
         <v>138000000</v>
       </c>
-      <c r="F27" s="12">
-        <f t="shared" si="3"/>
+      <c r="F27" s="14" t="n">
+        <f aca="false">E27+ng_FC</f>
         <v>268000000</v>
       </c>
-      <c r="G27" s="12">
-        <f t="shared" si="4"/>
+      <c r="G27" s="14" t="n">
+        <f aca="false">D27-F27</f>
         <v>92000000</v>
       </c>
-      <c r="H27" s="11">
-        <f t="shared" si="5"/>
+      <c r="H27" s="13" t="n">
+        <f aca="false">(D27-D26)/(B27-B26)</f>
         <v>120</v>
       </c>
-      <c r="I27" s="11">
-        <f t="shared" si="6"/>
+      <c r="I27" s="13" t="n">
+        <f aca="false">(F27-F26)/(B27-B26)</f>
         <v>83.5</v>
       </c>
-      <c r="J27" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J27" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I27,ng_P&lt;=I28),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K27" s="14">
-        <f t="shared" si="8"/>
+      <c r="K27" s="16" t="n">
+        <f aca="false">(B27+B26)/2</f>
         <v>2750000</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B28" s="14">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="16" t="n">
         <v>3500000</v>
       </c>
-      <c r="C28" s="12">
-        <f t="shared" si="0"/>
+      <c r="C28" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D28" s="12">
-        <f t="shared" si="1"/>
+      <c r="D28" s="14" t="n">
+        <f aca="false">C28*B28</f>
         <v>420000000</v>
       </c>
-      <c r="E28" s="12">
-        <f t="shared" si="2"/>
+      <c r="E28" s="14" t="n">
+        <f aca="false">ng_a*B28+ng_b*B28^2</f>
         <v>187250000</v>
       </c>
-      <c r="F28" s="12">
-        <f t="shared" si="3"/>
+      <c r="F28" s="14" t="n">
+        <f aca="false">E28+ng_FC</f>
         <v>317250000</v>
       </c>
-      <c r="G28" s="12">
-        <f t="shared" si="4"/>
+      <c r="G28" s="14" t="n">
+        <f aca="false">D28-F28</f>
         <v>102750000</v>
       </c>
-      <c r="H28" s="11">
-        <f t="shared" si="5"/>
+      <c r="H28" s="13" t="n">
+        <f aca="false">(D28-D27)/(B28-B27)</f>
         <v>120</v>
       </c>
-      <c r="I28" s="11">
-        <f t="shared" si="6"/>
+      <c r="I28" s="13" t="n">
+        <f aca="false">(F28-F27)/(B28-B27)</f>
         <v>98.5</v>
       </c>
-      <c r="J28" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J28" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I28,ng_P&lt;=I29),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K28" s="14">
-        <f t="shared" si="8"/>
+      <c r="K28" s="16" t="n">
+        <f aca="false">(B28+B27)/2</f>
         <v>3250000</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B29" s="14">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="16" t="n">
         <v>4000000</v>
       </c>
-      <c r="C29" s="12">
-        <f t="shared" si="0"/>
+      <c r="C29" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D29" s="12">
-        <f t="shared" si="1"/>
+      <c r="D29" s="14" t="n">
+        <f aca="false">C29*B29</f>
         <v>480000000</v>
       </c>
-      <c r="E29" s="12">
-        <f t="shared" si="2"/>
+      <c r="E29" s="14" t="n">
+        <f aca="false">ng_a*B29+ng_b*B29^2</f>
         <v>244000000</v>
       </c>
-      <c r="F29" s="12">
-        <f t="shared" si="3"/>
+      <c r="F29" s="14" t="n">
+        <f aca="false">E29+ng_FC</f>
         <v>374000000</v>
       </c>
-      <c r="G29" s="12">
-        <f t="shared" si="4"/>
+      <c r="G29" s="14" t="n">
+        <f aca="false">D29-F29</f>
         <v>106000000</v>
       </c>
-      <c r="H29" s="11">
-        <f t="shared" si="5"/>
+      <c r="H29" s="13" t="n">
+        <f aca="false">(D29-D28)/(B29-B28)</f>
         <v>120</v>
       </c>
-      <c r="I29" s="11">
-        <f t="shared" si="6"/>
+      <c r="I29" s="13" t="n">
+        <f aca="false">(F29-F28)/(B29-B28)</f>
         <v>113.5</v>
       </c>
-      <c r="J29" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J29" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I29,ng_P&lt;=I30),"&lt;-- P ~ MC","")</f>
         <v>&lt;-- P ~ MC</v>
       </c>
-      <c r="K29" s="14">
-        <f t="shared" si="8"/>
+      <c r="K29" s="16" t="n">
+        <f aca="false">(B29+B28)/2</f>
         <v>3750000</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B30" s="14">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="16" t="n">
         <v>4500000</v>
       </c>
-      <c r="C30" s="12">
-        <f t="shared" si="0"/>
+      <c r="C30" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D30" s="12">
-        <f t="shared" si="1"/>
+      <c r="D30" s="14" t="n">
+        <f aca="false">C30*B30</f>
         <v>540000000</v>
       </c>
-      <c r="E30" s="12">
-        <f t="shared" si="2"/>
+      <c r="E30" s="14" t="n">
+        <f aca="false">ng_a*B30+ng_b*B30^2</f>
         <v>308250000</v>
       </c>
-      <c r="F30" s="12">
-        <f t="shared" si="3"/>
+      <c r="F30" s="14" t="n">
+        <f aca="false">E30+ng_FC</f>
         <v>438250000</v>
       </c>
-      <c r="G30" s="12">
-        <f t="shared" si="4"/>
+      <c r="G30" s="14" t="n">
+        <f aca="false">D30-F30</f>
         <v>101750000</v>
       </c>
-      <c r="H30" s="11">
-        <f t="shared" si="5"/>
+      <c r="H30" s="13" t="n">
+        <f aca="false">(D30-D29)/(B30-B29)</f>
         <v>120</v>
       </c>
-      <c r="I30" s="11">
-        <f t="shared" si="6"/>
+      <c r="I30" s="13" t="n">
+        <f aca="false">(F30-F29)/(B30-B29)</f>
         <v>128.5</v>
       </c>
-      <c r="J30" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J30" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I30,ng_P&lt;=I31),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K30" s="14">
-        <f t="shared" si="8"/>
+      <c r="K30" s="16" t="n">
+        <f aca="false">(B30+B29)/2</f>
         <v>4250000</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B31" s="14">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="16" t="n">
         <v>5000000</v>
       </c>
-      <c r="C31" s="12">
-        <f t="shared" si="0"/>
+      <c r="C31" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D31" s="12">
-        <f t="shared" si="1"/>
+      <c r="D31" s="14" t="n">
+        <f aca="false">C31*B31</f>
         <v>600000000</v>
       </c>
-      <c r="E31" s="12">
-        <f t="shared" si="2"/>
+      <c r="E31" s="14" t="n">
+        <f aca="false">ng_a*B31+ng_b*B31^2</f>
         <v>380000000</v>
       </c>
-      <c r="F31" s="12">
-        <f t="shared" si="3"/>
+      <c r="F31" s="14" t="n">
+        <f aca="false">E31+ng_FC</f>
         <v>510000000</v>
       </c>
-      <c r="G31" s="12">
-        <f t="shared" si="4"/>
+      <c r="G31" s="14" t="n">
+        <f aca="false">D31-F31</f>
         <v>90000000</v>
       </c>
-      <c r="H31" s="11">
-        <f t="shared" si="5"/>
+      <c r="H31" s="13" t="n">
+        <f aca="false">(D31-D30)/(B31-B30)</f>
         <v>120</v>
       </c>
-      <c r="I31" s="11">
-        <f t="shared" si="6"/>
+      <c r="I31" s="13" t="n">
+        <f aca="false">(F31-F30)/(B31-B30)</f>
         <v>143.5</v>
       </c>
-      <c r="J31" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J31" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I31,ng_P&lt;=I32),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K31" s="14">
-        <f t="shared" si="8"/>
+      <c r="K31" s="16" t="n">
+        <f aca="false">(B31+B30)/2</f>
         <v>4750000</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B32" s="14">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="16" t="n">
         <v>5500000</v>
       </c>
-      <c r="C32" s="12">
-        <f t="shared" si="0"/>
+      <c r="C32" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D32" s="12">
-        <f t="shared" si="1"/>
+      <c r="D32" s="14" t="n">
+        <f aca="false">C32*B32</f>
         <v>660000000</v>
       </c>
-      <c r="E32" s="12">
-        <f t="shared" si="2"/>
+      <c r="E32" s="14" t="n">
+        <f aca="false">ng_a*B32+ng_b*B32^2</f>
         <v>459250000</v>
       </c>
-      <c r="F32" s="12">
-        <f t="shared" si="3"/>
+      <c r="F32" s="14" t="n">
+        <f aca="false">E32+ng_FC</f>
         <v>589250000</v>
       </c>
-      <c r="G32" s="12">
-        <f t="shared" si="4"/>
+      <c r="G32" s="14" t="n">
+        <f aca="false">D32-F32</f>
         <v>70750000</v>
       </c>
-      <c r="H32" s="11">
-        <f t="shared" si="5"/>
+      <c r="H32" s="13" t="n">
+        <f aca="false">(D32-D31)/(B32-B31)</f>
         <v>120</v>
       </c>
-      <c r="I32" s="11">
-        <f t="shared" si="6"/>
+      <c r="I32" s="13" t="n">
+        <f aca="false">(F32-F31)/(B32-B31)</f>
         <v>158.5</v>
       </c>
-      <c r="J32" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J32" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I32,ng_P&lt;=I33),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K32" s="14">
-        <f t="shared" si="8"/>
+      <c r="K32" s="16" t="n">
+        <f aca="false">(B32+B31)/2</f>
         <v>5250000</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B33" s="14">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="16" t="n">
         <v>6000000</v>
       </c>
-      <c r="C33" s="12">
-        <f t="shared" si="0"/>
+      <c r="C33" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D33" s="12">
-        <f t="shared" si="1"/>
+      <c r="D33" s="14" t="n">
+        <f aca="false">C33*B33</f>
         <v>720000000</v>
       </c>
-      <c r="E33" s="12">
-        <f t="shared" si="2"/>
+      <c r="E33" s="14" t="n">
+        <f aca="false">ng_a*B33+ng_b*B33^2</f>
         <v>546000000</v>
       </c>
-      <c r="F33" s="12">
-        <f t="shared" si="3"/>
+      <c r="F33" s="14" t="n">
+        <f aca="false">E33+ng_FC</f>
         <v>676000000</v>
       </c>
-      <c r="G33" s="12">
-        <f t="shared" si="4"/>
+      <c r="G33" s="14" t="n">
+        <f aca="false">D33-F33</f>
         <v>44000000</v>
       </c>
-      <c r="H33" s="11">
-        <f t="shared" si="5"/>
+      <c r="H33" s="13" t="n">
+        <f aca="false">(D33-D32)/(B33-B32)</f>
         <v>120</v>
       </c>
-      <c r="I33" s="11">
-        <f t="shared" si="6"/>
+      <c r="I33" s="13" t="n">
+        <f aca="false">(F33-F32)/(B33-B32)</f>
         <v>173.5</v>
       </c>
-      <c r="J33" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J33" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I33,ng_P&lt;=I34),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K33" s="14">
-        <f t="shared" si="8"/>
+      <c r="K33" s="16" t="n">
+        <f aca="false">(B33+B32)/2</f>
         <v>5750000</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B34" s="14">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="16" t="n">
         <v>6500000</v>
       </c>
-      <c r="C34" s="12">
-        <f t="shared" si="0"/>
+      <c r="C34" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D34" s="12">
-        <f t="shared" si="1"/>
+      <c r="D34" s="14" t="n">
+        <f aca="false">C34*B34</f>
         <v>780000000</v>
       </c>
-      <c r="E34" s="12">
-        <f t="shared" si="2"/>
+      <c r="E34" s="14" t="n">
+        <f aca="false">ng_a*B34+ng_b*B34^2</f>
         <v>640250000</v>
       </c>
-      <c r="F34" s="12">
-        <f t="shared" si="3"/>
+      <c r="F34" s="14" t="n">
+        <f aca="false">E34+ng_FC</f>
         <v>770250000</v>
       </c>
-      <c r="G34" s="12">
-        <f t="shared" si="4"/>
+      <c r="G34" s="14" t="n">
+        <f aca="false">D34-F34</f>
         <v>9750000</v>
       </c>
-      <c r="H34" s="11">
-        <f t="shared" si="5"/>
+      <c r="H34" s="13" t="n">
+        <f aca="false">(D34-D33)/(B34-B33)</f>
         <v>120</v>
       </c>
-      <c r="I34" s="11">
-        <f t="shared" si="6"/>
+      <c r="I34" s="13" t="n">
+        <f aca="false">(F34-F33)/(B34-B33)</f>
         <v>188.5</v>
       </c>
-      <c r="J34" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J34" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I34,ng_P&lt;=I35),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K34" s="14">
-        <f t="shared" si="8"/>
+      <c r="K34" s="16" t="n">
+        <f aca="false">(B34+B33)/2</f>
         <v>6250000</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B35" s="14">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="16" t="n">
         <v>7000000</v>
       </c>
-      <c r="C35" s="12">
-        <f t="shared" si="0"/>
+      <c r="C35" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D35" s="12">
-        <f t="shared" si="1"/>
+      <c r="D35" s="14" t="n">
+        <f aca="false">C35*B35</f>
         <v>840000000</v>
       </c>
-      <c r="E35" s="12">
-        <f t="shared" si="2"/>
+      <c r="E35" s="14" t="n">
+        <f aca="false">ng_a*B35+ng_b*B35^2</f>
         <v>742000000</v>
       </c>
-      <c r="F35" s="12">
-        <f t="shared" si="3"/>
+      <c r="F35" s="14" t="n">
+        <f aca="false">E35+ng_FC</f>
         <v>872000000</v>
       </c>
-      <c r="G35" s="12">
-        <f t="shared" si="4"/>
+      <c r="G35" s="14" t="n">
+        <f aca="false">D35-F35</f>
         <v>-32000000</v>
       </c>
-      <c r="H35" s="11">
-        <f t="shared" si="5"/>
+      <c r="H35" s="13" t="n">
+        <f aca="false">(D35-D34)/(B35-B34)</f>
         <v>120</v>
       </c>
-      <c r="I35" s="11">
-        <f t="shared" si="6"/>
+      <c r="I35" s="13" t="n">
+        <f aca="false">(F35-F34)/(B35-B34)</f>
         <v>203.5</v>
       </c>
-      <c r="J35" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J35" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I35,ng_P&lt;=I36),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K35" s="14">
-        <f t="shared" si="8"/>
+      <c r="K35" s="16" t="n">
+        <f aca="false">(B35+B34)/2</f>
         <v>6750000</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B36" s="14">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="16" t="n">
         <v>7500000</v>
       </c>
-      <c r="C36" s="12">
-        <f t="shared" si="0"/>
+      <c r="C36" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D36" s="12">
-        <f t="shared" si="1"/>
+      <c r="D36" s="14" t="n">
+        <f aca="false">C36*B36</f>
         <v>900000000</v>
       </c>
-      <c r="E36" s="12">
-        <f t="shared" si="2"/>
+      <c r="E36" s="14" t="n">
+        <f aca="false">ng_a*B36+ng_b*B36^2</f>
         <v>851250000</v>
       </c>
-      <c r="F36" s="12">
-        <f t="shared" si="3"/>
+      <c r="F36" s="14" t="n">
+        <f aca="false">E36+ng_FC</f>
         <v>981250000</v>
       </c>
-      <c r="G36" s="12">
-        <f t="shared" si="4"/>
+      <c r="G36" s="14" t="n">
+        <f aca="false">D36-F36</f>
         <v>-81250000</v>
       </c>
-      <c r="H36" s="11">
-        <f t="shared" si="5"/>
+      <c r="H36" s="13" t="n">
+        <f aca="false">(D36-D35)/(B36-B35)</f>
         <v>120</v>
       </c>
-      <c r="I36" s="11">
-        <f t="shared" si="6"/>
+      <c r="I36" s="13" t="n">
+        <f aca="false">(F36-F35)/(B36-B35)</f>
         <v>218.5</v>
       </c>
-      <c r="J36" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J36" s="5" t="str">
+        <f aca="false">IF(AND(ng_P&gt;I36,ng_P&lt;=I37),"&lt;-- P ~ MC","")</f>
         <v/>
       </c>
-      <c r="K36" s="14">
-        <f t="shared" si="8"/>
+      <c r="K36" s="16" t="n">
+        <f aca="false">(B36+B35)/2</f>
         <v>7250000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B37" s="14">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="16" t="n">
         <v>8000000</v>
       </c>
-      <c r="C37" s="12">
-        <f t="shared" si="0"/>
+      <c r="C37" s="14" t="n">
+        <f aca="false">ng_P</f>
         <v>120</v>
       </c>
-      <c r="D37" s="12">
-        <f t="shared" si="1"/>
+      <c r="D37" s="14" t="n">
+        <f aca="false">C37*B37</f>
         <v>960000000</v>
       </c>
-      <c r="E37" s="12">
-        <f t="shared" si="2"/>
+      <c r="E37" s="14" t="n">
+        <f aca="false">ng_a*B37+ng_b*B37^2</f>
         <v>968000000</v>
       </c>
-      <c r="F37" s="12">
-        <f t="shared" si="3"/>
+      <c r="F37" s="14" t="n">
+        <f aca="false">E37+ng_FC</f>
         <v>1098000000</v>
       </c>
-      <c r="G37" s="12">
-        <f t="shared" si="4"/>
+      <c r="G37" s="14" t="n">
+        <f aca="false">D37-F37</f>
         <v>-138000000</v>
       </c>
-      <c r="H37" s="11">
-        <f t="shared" si="5"/>
+      <c r="H37" s="13" t="n">
+        <f aca="false">(D37-D36)/(B37-B36)</f>
         <v>120</v>
       </c>
-      <c r="I37" s="11">
-        <f t="shared" si="6"/>
+      <c r="I37" s="13" t="n">
+        <f aca="false">(F37-F36)/(B37-B36)</f>
         <v>233.5</v>
       </c>
-      <c r="K37" s="14">
-        <f t="shared" si="8"/>
+      <c r="K37" s="16" t="n">
+        <f aca="false">(B37+B36)/2</f>
         <v>7750000</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:K59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>-6.7E-006</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>1E-006</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <f aca="false">g_Di</f>
+        <v>525</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">2*g_Ds</f>
+        <v>-1.34E-005</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <f aca="false">g_Di+2*g_Ds*g_Qopt</f>
+        <v>525</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <f aca="false">g_a+2*g_b*g_Qopt</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <f aca="false">g_Popt*g_Qopt</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <f aca="false">g_a*g_Qopt+g_b*g_Qopt^2</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <f aca="false">g_a*g_Qopt+g_b*g_Qopt^2+g_FC</f>
+        <v>130000000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <f aca="false">g_Popt*g_Qopt-(g_a*g_Qopt+g_b*g_Qopt^2+g_FC)</f>
+        <v>-130000000</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <f aca="false">g_Popt/(g_a+2*g_b*g_Qopt)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="20" t="str">
+        <f aca="false">IFERROR((g_Popt-(g_a+2*g_b*g_Qopt))/g_Popt,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <f aca="false">(g_Di-g_a)/(2*g_b-g_Ds)</f>
+        <v>60229885.0574713</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*((g_Di-g_a)/(2*g_b-g_Ds))</f>
+        <v>121.459770114943</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="14" t="str">
+        <f aca="false">IF(g_Qopt=0,"—",0.5*(g_Popt-(g_a+2*g_b*g_Qopt))*(((g_Di-g_a)/(2*g_b-g_Ds))-g_Qopt))</f>
+        <v>—</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="15" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="6" t="s">
+      <c r="I34" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="7">
+      <c r="J34" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B35</f>
         <v>525</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="9">
-        <v>-6.7000000000000002E-6</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="9">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="D35" s="14" t="n">
+        <f aca="false">C35*B35</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <f aca="false">g_a*B35+g_b*B35^2</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <f aca="false">E35+g_FC</f>
         <v>130000000</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="12">
-        <f>g_Di</f>
-        <v>525</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="15">
-        <f>2*g_Ds</f>
-        <v>-1.34E-5</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="10">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="16">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="11">
-        <f>g_Di+2*g_Ds*g_Qopt</f>
-        <v>525</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="11">
-        <f>g_a+2*g_b*g_Qopt</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="12">
-        <f>g_Popt*g_Qopt</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="12">
-        <f>g_a*g_Qopt+g_b*g_Qopt^2</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="12">
-        <f>g_a*g_Qopt+g_b*g_Qopt^2+g_FC</f>
-        <v>130000000</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="12">
-        <f>g_Popt*g_Qopt-(g_a*g_Qopt+g_b*g_Qopt^2+g_FC)</f>
+      <c r="G35" s="14" t="n">
+        <f aca="false">D35-F35</f>
         <v>-130000000</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="17">
-        <f>g_Popt/(g_a+2*g_b*g_Qopt)</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="18" t="str">
-        <f>IFERROR((g_Popt-(g_a+2*g_b*g_Qopt))/g_Popt,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="14">
-        <f>(g_Di-g_a)/(2*g_b-g_Ds)</f>
-        <v>60229885.057471268</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B30" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="11">
-        <f>g_Di+g_Ds*((g_Di-g_a)/(2*g_b-g_Ds))</f>
-        <v>121.4597701149425</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="12">
-        <f>0.5*(g_Popt-(g_a+2*g_b*g_Qopt))*(((g_Di-g_a)/(2*g_b-g_Ds))-g_Qopt)</f>
-        <v>-30114942.528735634</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B33" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B34" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B35" s="14">
-        <v>0</v>
-      </c>
-      <c r="C35" s="11">
-        <f t="shared" ref="C35:C59" si="0">g_Di+g_Ds*B35</f>
-        <v>525</v>
-      </c>
-      <c r="D35" s="12">
-        <f t="shared" ref="D35:D59" si="1">C35*B35</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="12">
-        <f t="shared" ref="E35:E59" si="2">g_a*B35+g_b*B35^2</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="12">
-        <f t="shared" ref="F35:F59" si="3">E35+g_FC</f>
-        <v>130000000</v>
-      </c>
-      <c r="G35" s="12">
-        <f t="shared" ref="G35:G59" si="4">D35-F35</f>
-        <v>-130000000</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B36" s="14">
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="16" t="n">
         <v>2500000</v>
       </c>
-      <c r="C36" s="11">
-        <f t="shared" si="0"/>
+      <c r="C36" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B36</f>
         <v>508.25</v>
       </c>
-      <c r="D36" s="12">
-        <f t="shared" si="1"/>
+      <c r="D36" s="14" t="n">
+        <f aca="false">C36*B36</f>
         <v>1270625000</v>
       </c>
-      <c r="E36" s="12">
-        <f t="shared" si="2"/>
+      <c r="E36" s="14" t="n">
+        <f aca="false">g_a*B36+g_b*B36^2</f>
         <v>8750000</v>
       </c>
-      <c r="F36" s="12">
-        <f t="shared" si="3"/>
+      <c r="F36" s="14" t="n">
+        <f aca="false">E36+g_FC</f>
         <v>138750000</v>
       </c>
-      <c r="G36" s="12">
-        <f t="shared" si="4"/>
+      <c r="G36" s="14" t="n">
+        <f aca="false">D36-F36</f>
         <v>1131875000</v>
       </c>
-      <c r="H36" s="11">
-        <f t="shared" ref="H36:H59" si="5">(D36-D35)/(B36-B35)</f>
+      <c r="H36" s="13" t="n">
+        <f aca="false">(D36-D35)/(B36-B35)</f>
         <v>508.25</v>
       </c>
-      <c r="I36" s="11">
-        <f t="shared" ref="I36:I59" si="6">(F36-F35)/(B36-B35)</f>
+      <c r="I36" s="13" t="n">
+        <f aca="false">(F36-F35)/(B36-B35)</f>
         <v>3.5</v>
       </c>
-      <c r="J36" s="6" t="str">
-        <f t="shared" ref="J36:J58" si="7">IF(AND(H36&gt;I36,H37&lt;=I37),"&lt;-- MR ~ MC","")</f>
+      <c r="J36" s="5" t="str">
+        <f aca="false">IF(AND(H36&gt;I36,H37&lt;=I37),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K36" s="14">
-        <f t="shared" ref="K36:K59" si="8">(B36+B35)/2</f>
+      <c r="K36" s="16" t="n">
+        <f aca="false">(B36+B35)/2</f>
         <v>1250000</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B37" s="14">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="16" t="n">
         <v>5000000</v>
       </c>
-      <c r="C37" s="11">
-        <f t="shared" si="0"/>
+      <c r="C37" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B37</f>
         <v>491.5</v>
       </c>
-      <c r="D37" s="12">
-        <f t="shared" si="1"/>
+      <c r="D37" s="14" t="n">
+        <f aca="false">C37*B37</f>
         <v>2457500000</v>
       </c>
-      <c r="E37" s="12">
-        <f t="shared" si="2"/>
+      <c r="E37" s="14" t="n">
+        <f aca="false">g_a*B37+g_b*B37^2</f>
         <v>30000000</v>
       </c>
-      <c r="F37" s="12">
-        <f t="shared" si="3"/>
+      <c r="F37" s="14" t="n">
+        <f aca="false">E37+g_FC</f>
         <v>160000000</v>
       </c>
-      <c r="G37" s="12">
-        <f t="shared" si="4"/>
+      <c r="G37" s="14" t="n">
+        <f aca="false">D37-F37</f>
         <v>2297500000</v>
       </c>
-      <c r="H37" s="11">
-        <f t="shared" si="5"/>
+      <c r="H37" s="13" t="n">
+        <f aca="false">(D37-D36)/(B37-B36)</f>
         <v>474.75</v>
       </c>
-      <c r="I37" s="11">
-        <f t="shared" si="6"/>
+      <c r="I37" s="13" t="n">
+        <f aca="false">(F37-F36)/(B37-B36)</f>
         <v>8.5</v>
       </c>
-      <c r="J37" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J37" s="5" t="str">
+        <f aca="false">IF(AND(H37&gt;I37,H38&lt;=I38),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K37" s="14">
-        <f t="shared" si="8"/>
+      <c r="K37" s="16" t="n">
+        <f aca="false">(B37+B36)/2</f>
         <v>3750000</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B38" s="14">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="16" t="n">
         <v>7500000</v>
       </c>
-      <c r="C38" s="11">
-        <f t="shared" si="0"/>
+      <c r="C38" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B38</f>
         <v>474.75</v>
       </c>
-      <c r="D38" s="12">
-        <f t="shared" si="1"/>
+      <c r="D38" s="14" t="n">
+        <f aca="false">C38*B38</f>
         <v>3560625000</v>
       </c>
-      <c r="E38" s="12">
-        <f t="shared" si="2"/>
+      <c r="E38" s="14" t="n">
+        <f aca="false">g_a*B38+g_b*B38^2</f>
         <v>63750000</v>
       </c>
-      <c r="F38" s="12">
-        <f t="shared" si="3"/>
+      <c r="F38" s="14" t="n">
+        <f aca="false">E38+g_FC</f>
         <v>193750000</v>
       </c>
-      <c r="G38" s="12">
-        <f t="shared" si="4"/>
+      <c r="G38" s="14" t="n">
+        <f aca="false">D38-F38</f>
         <v>3366875000</v>
       </c>
-      <c r="H38" s="11">
-        <f t="shared" si="5"/>
+      <c r="H38" s="13" t="n">
+        <f aca="false">(D38-D37)/(B38-B37)</f>
         <v>441.25</v>
       </c>
-      <c r="I38" s="11">
-        <f t="shared" si="6"/>
+      <c r="I38" s="13" t="n">
+        <f aca="false">(F38-F37)/(B38-B37)</f>
         <v>13.5</v>
       </c>
-      <c r="J38" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J38" s="5" t="str">
+        <f aca="false">IF(AND(H38&gt;I38,H39&lt;=I39),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K38" s="14">
-        <f t="shared" si="8"/>
+      <c r="K38" s="16" t="n">
+        <f aca="false">(B38+B37)/2</f>
         <v>6250000</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B39" s="14">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="16" t="n">
         <v>10000000</v>
       </c>
-      <c r="C39" s="11">
-        <f t="shared" si="0"/>
+      <c r="C39" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B39</f>
         <v>458</v>
       </c>
-      <c r="D39" s="12">
-        <f t="shared" si="1"/>
+      <c r="D39" s="14" t="n">
+        <f aca="false">C39*B39</f>
         <v>4580000000</v>
       </c>
-      <c r="E39" s="12">
-        <f t="shared" si="2"/>
+      <c r="E39" s="14" t="n">
+        <f aca="false">g_a*B39+g_b*B39^2</f>
         <v>110000000</v>
       </c>
-      <c r="F39" s="12">
-        <f t="shared" si="3"/>
+      <c r="F39" s="14" t="n">
+        <f aca="false">E39+g_FC</f>
         <v>240000000</v>
       </c>
-      <c r="G39" s="12">
-        <f t="shared" si="4"/>
+      <c r="G39" s="14" t="n">
+        <f aca="false">D39-F39</f>
         <v>4340000000</v>
       </c>
-      <c r="H39" s="11">
-        <f t="shared" si="5"/>
+      <c r="H39" s="13" t="n">
+        <f aca="false">(D39-D38)/(B39-B38)</f>
         <v>407.75</v>
       </c>
-      <c r="I39" s="11">
-        <f t="shared" si="6"/>
+      <c r="I39" s="13" t="n">
+        <f aca="false">(F39-F38)/(B39-B38)</f>
         <v>18.5</v>
       </c>
-      <c r="J39" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J39" s="5" t="str">
+        <f aca="false">IF(AND(H39&gt;I39,H40&lt;=I40),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K39" s="14">
-        <f t="shared" si="8"/>
+      <c r="K39" s="16" t="n">
+        <f aca="false">(B39+B38)/2</f>
         <v>8750000</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B40" s="14">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="16" t="n">
         <v>12500000</v>
       </c>
-      <c r="C40" s="11">
-        <f t="shared" si="0"/>
+      <c r="C40" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B40</f>
         <v>441.25</v>
       </c>
-      <c r="D40" s="12">
-        <f t="shared" si="1"/>
+      <c r="D40" s="14" t="n">
+        <f aca="false">C40*B40</f>
         <v>5515625000</v>
       </c>
-      <c r="E40" s="12">
-        <f t="shared" si="2"/>
+      <c r="E40" s="14" t="n">
+        <f aca="false">g_a*B40+g_b*B40^2</f>
         <v>168750000</v>
       </c>
-      <c r="F40" s="12">
-        <f t="shared" si="3"/>
+      <c r="F40" s="14" t="n">
+        <f aca="false">E40+g_FC</f>
         <v>298750000</v>
       </c>
-      <c r="G40" s="12">
-        <f t="shared" si="4"/>
+      <c r="G40" s="14" t="n">
+        <f aca="false">D40-F40</f>
         <v>5216875000</v>
       </c>
-      <c r="H40" s="11">
-        <f t="shared" si="5"/>
+      <c r="H40" s="13" t="n">
+        <f aca="false">(D40-D39)/(B40-B39)</f>
         <v>374.25</v>
       </c>
-      <c r="I40" s="11">
-        <f t="shared" si="6"/>
+      <c r="I40" s="13" t="n">
+        <f aca="false">(F40-F39)/(B40-B39)</f>
         <v>23.5</v>
       </c>
-      <c r="J40" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J40" s="5" t="str">
+        <f aca="false">IF(AND(H40&gt;I40,H41&lt;=I41),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K40" s="14">
-        <f t="shared" si="8"/>
+      <c r="K40" s="16" t="n">
+        <f aca="false">(B40+B39)/2</f>
         <v>11250000</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B41" s="14">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="16" t="n">
         <v>15000000</v>
       </c>
-      <c r="C41" s="11">
-        <f t="shared" si="0"/>
+      <c r="C41" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B41</f>
         <v>424.5</v>
       </c>
-      <c r="D41" s="12">
-        <f t="shared" si="1"/>
+      <c r="D41" s="14" t="n">
+        <f aca="false">C41*B41</f>
         <v>6367500000</v>
       </c>
-      <c r="E41" s="12">
-        <f t="shared" si="2"/>
+      <c r="E41" s="14" t="n">
+        <f aca="false">g_a*B41+g_b*B41^2</f>
         <v>240000000</v>
       </c>
-      <c r="F41" s="12">
-        <f t="shared" si="3"/>
+      <c r="F41" s="14" t="n">
+        <f aca="false">E41+g_FC</f>
         <v>370000000</v>
       </c>
-      <c r="G41" s="12">
-        <f t="shared" si="4"/>
+      <c r="G41" s="14" t="n">
+        <f aca="false">D41-F41</f>
         <v>5997500000</v>
       </c>
-      <c r="H41" s="11">
-        <f t="shared" si="5"/>
+      <c r="H41" s="13" t="n">
+        <f aca="false">(D41-D40)/(B41-B40)</f>
         <v>340.75</v>
       </c>
-      <c r="I41" s="11">
-        <f t="shared" si="6"/>
+      <c r="I41" s="13" t="n">
+        <f aca="false">(F41-F40)/(B41-B40)</f>
         <v>28.5</v>
       </c>
-      <c r="J41" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J41" s="5" t="str">
+        <f aca="false">IF(AND(H41&gt;I41,H42&lt;=I42),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K41" s="14">
-        <f t="shared" si="8"/>
+      <c r="K41" s="16" t="n">
+        <f aca="false">(B41+B40)/2</f>
         <v>13750000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B42" s="14">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="16" t="n">
         <v>17500000</v>
       </c>
-      <c r="C42" s="11">
-        <f t="shared" si="0"/>
+      <c r="C42" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B42</f>
         <v>407.75</v>
       </c>
-      <c r="D42" s="12">
-        <f t="shared" si="1"/>
+      <c r="D42" s="14" t="n">
+        <f aca="false">C42*B42</f>
         <v>7135625000</v>
       </c>
-      <c r="E42" s="12">
-        <f t="shared" si="2"/>
+      <c r="E42" s="14" t="n">
+        <f aca="false">g_a*B42+g_b*B42^2</f>
         <v>323750000</v>
       </c>
-      <c r="F42" s="12">
-        <f t="shared" si="3"/>
+      <c r="F42" s="14" t="n">
+        <f aca="false">E42+g_FC</f>
         <v>453750000</v>
       </c>
-      <c r="G42" s="12">
-        <f t="shared" si="4"/>
+      <c r="G42" s="14" t="n">
+        <f aca="false">D42-F42</f>
         <v>6681875000</v>
       </c>
-      <c r="H42" s="11">
-        <f t="shared" si="5"/>
+      <c r="H42" s="13" t="n">
+        <f aca="false">(D42-D41)/(B42-B41)</f>
         <v>307.25</v>
       </c>
-      <c r="I42" s="11">
-        <f t="shared" si="6"/>
+      <c r="I42" s="13" t="n">
+        <f aca="false">(F42-F41)/(B42-B41)</f>
         <v>33.5</v>
       </c>
-      <c r="J42" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J42" s="5" t="str">
+        <f aca="false">IF(AND(H42&gt;I42,H43&lt;=I43),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K42" s="14">
-        <f t="shared" si="8"/>
+      <c r="K42" s="16" t="n">
+        <f aca="false">(B42+B41)/2</f>
         <v>16250000</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B43" s="14">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="16" t="n">
         <v>20000000</v>
       </c>
-      <c r="C43" s="11">
-        <f t="shared" si="0"/>
+      <c r="C43" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B43</f>
         <v>391</v>
       </c>
-      <c r="D43" s="12">
-        <f t="shared" si="1"/>
+      <c r="D43" s="14" t="n">
+        <f aca="false">C43*B43</f>
         <v>7820000000</v>
       </c>
-      <c r="E43" s="12">
-        <f t="shared" si="2"/>
+      <c r="E43" s="14" t="n">
+        <f aca="false">g_a*B43+g_b*B43^2</f>
         <v>420000000</v>
       </c>
-      <c r="F43" s="12">
-        <f t="shared" si="3"/>
+      <c r="F43" s="14" t="n">
+        <f aca="false">E43+g_FC</f>
         <v>550000000</v>
       </c>
-      <c r="G43" s="12">
-        <f t="shared" si="4"/>
+      <c r="G43" s="14" t="n">
+        <f aca="false">D43-F43</f>
         <v>7270000000</v>
       </c>
-      <c r="H43" s="11">
-        <f t="shared" si="5"/>
+      <c r="H43" s="13" t="n">
+        <f aca="false">(D43-D42)/(B43-B42)</f>
         <v>273.75</v>
       </c>
-      <c r="I43" s="11">
-        <f t="shared" si="6"/>
+      <c r="I43" s="13" t="n">
+        <f aca="false">(F43-F42)/(B43-B42)</f>
         <v>38.5</v>
       </c>
-      <c r="J43" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J43" s="5" t="str">
+        <f aca="false">IF(AND(H43&gt;I43,H44&lt;=I44),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K43" s="14">
-        <f t="shared" si="8"/>
+      <c r="K43" s="16" t="n">
+        <f aca="false">(B43+B42)/2</f>
         <v>18750000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B44" s="14">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="16" t="n">
         <v>22500000</v>
       </c>
-      <c r="C44" s="11">
-        <f t="shared" si="0"/>
+      <c r="C44" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B44</f>
         <v>374.25</v>
       </c>
-      <c r="D44" s="12">
-        <f t="shared" si="1"/>
+      <c r="D44" s="14" t="n">
+        <f aca="false">C44*B44</f>
         <v>8420625000</v>
       </c>
-      <c r="E44" s="12">
-        <f t="shared" si="2"/>
+      <c r="E44" s="14" t="n">
+        <f aca="false">g_a*B44+g_b*B44^2</f>
         <v>528750000</v>
       </c>
-      <c r="F44" s="12">
-        <f t="shared" si="3"/>
+      <c r="F44" s="14" t="n">
+        <f aca="false">E44+g_FC</f>
         <v>658750000</v>
       </c>
-      <c r="G44" s="12">
-        <f t="shared" si="4"/>
+      <c r="G44" s="14" t="n">
+        <f aca="false">D44-F44</f>
         <v>7761875000</v>
       </c>
-      <c r="H44" s="11">
-        <f t="shared" si="5"/>
+      <c r="H44" s="13" t="n">
+        <f aca="false">(D44-D43)/(B44-B43)</f>
         <v>240.25</v>
       </c>
-      <c r="I44" s="11">
-        <f t="shared" si="6"/>
+      <c r="I44" s="13" t="n">
+        <f aca="false">(F44-F43)/(B44-B43)</f>
         <v>43.5</v>
       </c>
-      <c r="J44" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J44" s="5" t="str">
+        <f aca="false">IF(AND(H44&gt;I44,H45&lt;=I45),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K44" s="14">
-        <f t="shared" si="8"/>
+      <c r="K44" s="16" t="n">
+        <f aca="false">(B44+B43)/2</f>
         <v>21250000</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="14">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="16" t="n">
         <v>25000000</v>
       </c>
-      <c r="C45" s="11">
-        <f t="shared" si="0"/>
+      <c r="C45" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B45</f>
         <v>357.5</v>
       </c>
-      <c r="D45" s="12">
-        <f t="shared" si="1"/>
+      <c r="D45" s="14" t="n">
+        <f aca="false">C45*B45</f>
         <v>8937500000</v>
       </c>
-      <c r="E45" s="12">
-        <f t="shared" si="2"/>
+      <c r="E45" s="14" t="n">
+        <f aca="false">g_a*B45+g_b*B45^2</f>
         <v>650000000</v>
       </c>
-      <c r="F45" s="12">
-        <f t="shared" si="3"/>
+      <c r="F45" s="14" t="n">
+        <f aca="false">E45+g_FC</f>
         <v>780000000</v>
       </c>
-      <c r="G45" s="12">
-        <f t="shared" si="4"/>
+      <c r="G45" s="14" t="n">
+        <f aca="false">D45-F45</f>
         <v>8157500000</v>
       </c>
-      <c r="H45" s="11">
-        <f t="shared" si="5"/>
+      <c r="H45" s="13" t="n">
+        <f aca="false">(D45-D44)/(B45-B44)</f>
         <v>206.75</v>
       </c>
-      <c r="I45" s="11">
-        <f t="shared" si="6"/>
+      <c r="I45" s="13" t="n">
+        <f aca="false">(F45-F44)/(B45-B44)</f>
         <v>48.5</v>
       </c>
-      <c r="J45" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J45" s="5" t="str">
+        <f aca="false">IF(AND(H45&gt;I45,H46&lt;=I46),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K45" s="14">
-        <f t="shared" si="8"/>
+      <c r="K45" s="16" t="n">
+        <f aca="false">(B45+B44)/2</f>
         <v>23750000</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B46" s="14">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="16" t="n">
         <v>27500000</v>
       </c>
-      <c r="C46" s="11">
-        <f t="shared" si="0"/>
+      <c r="C46" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B46</f>
         <v>340.75</v>
       </c>
-      <c r="D46" s="12">
-        <f t="shared" si="1"/>
+      <c r="D46" s="14" t="n">
+        <f aca="false">C46*B46</f>
         <v>9370625000</v>
       </c>
-      <c r="E46" s="12">
-        <f t="shared" si="2"/>
+      <c r="E46" s="14" t="n">
+        <f aca="false">g_a*B46+g_b*B46^2</f>
         <v>783750000</v>
       </c>
-      <c r="F46" s="12">
-        <f t="shared" si="3"/>
+      <c r="F46" s="14" t="n">
+        <f aca="false">E46+g_FC</f>
         <v>913750000</v>
       </c>
-      <c r="G46" s="12">
-        <f t="shared" si="4"/>
+      <c r="G46" s="14" t="n">
+        <f aca="false">D46-F46</f>
         <v>8456875000</v>
       </c>
-      <c r="H46" s="11">
-        <f t="shared" si="5"/>
+      <c r="H46" s="13" t="n">
+        <f aca="false">(D46-D45)/(B46-B45)</f>
         <v>173.25</v>
       </c>
-      <c r="I46" s="11">
-        <f t="shared" si="6"/>
+      <c r="I46" s="13" t="n">
+        <f aca="false">(F46-F45)/(B46-B45)</f>
         <v>53.5</v>
       </c>
-      <c r="J46" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J46" s="5" t="str">
+        <f aca="false">IF(AND(H46&gt;I46,H47&lt;=I47),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K46" s="14">
-        <f t="shared" si="8"/>
+      <c r="K46" s="16" t="n">
+        <f aca="false">(B46+B45)/2</f>
         <v>26250000</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B47" s="14">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="16" t="n">
         <v>30000000</v>
       </c>
-      <c r="C47" s="11">
-        <f t="shared" si="0"/>
+      <c r="C47" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B47</f>
         <v>324</v>
       </c>
-      <c r="D47" s="12">
-        <f t="shared" si="1"/>
+      <c r="D47" s="14" t="n">
+        <f aca="false">C47*B47</f>
         <v>9720000000</v>
       </c>
-      <c r="E47" s="12">
-        <f t="shared" si="2"/>
+      <c r="E47" s="14" t="n">
+        <f aca="false">g_a*B47+g_b*B47^2</f>
         <v>930000000</v>
       </c>
-      <c r="F47" s="12">
-        <f t="shared" si="3"/>
+      <c r="F47" s="14" t="n">
+        <f aca="false">E47+g_FC</f>
         <v>1060000000</v>
       </c>
-      <c r="G47" s="12">
-        <f t="shared" si="4"/>
+      <c r="G47" s="14" t="n">
+        <f aca="false">D47-F47</f>
         <v>8660000000</v>
       </c>
-      <c r="H47" s="11">
-        <f t="shared" si="5"/>
+      <c r="H47" s="13" t="n">
+        <f aca="false">(D47-D46)/(B47-B46)</f>
         <v>139.75</v>
       </c>
-      <c r="I47" s="11">
-        <f t="shared" si="6"/>
+      <c r="I47" s="13" t="n">
+        <f aca="false">(F47-F46)/(B47-B46)</f>
         <v>58.5</v>
       </c>
-      <c r="J47" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J47" s="5" t="str">
+        <f aca="false">IF(AND(H47&gt;I47,H48&lt;=I48),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K47" s="14">
-        <f t="shared" si="8"/>
+      <c r="K47" s="16" t="n">
+        <f aca="false">(B47+B46)/2</f>
         <v>28750000</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B48" s="14">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="16" t="n">
         <v>32500000</v>
       </c>
-      <c r="C48" s="11">
-        <f t="shared" si="0"/>
+      <c r="C48" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B48</f>
         <v>307.25</v>
       </c>
-      <c r="D48" s="12">
-        <f t="shared" si="1"/>
+      <c r="D48" s="14" t="n">
+        <f aca="false">C48*B48</f>
         <v>9985625000</v>
       </c>
-      <c r="E48" s="12">
-        <f t="shared" si="2"/>
+      <c r="E48" s="14" t="n">
+        <f aca="false">g_a*B48+g_b*B48^2</f>
         <v>1088750000</v>
       </c>
-      <c r="F48" s="12">
-        <f t="shared" si="3"/>
+      <c r="F48" s="14" t="n">
+        <f aca="false">E48+g_FC</f>
         <v>1218750000</v>
       </c>
-      <c r="G48" s="12">
-        <f t="shared" si="4"/>
+      <c r="G48" s="14" t="n">
+        <f aca="false">D48-F48</f>
         <v>8766875000</v>
       </c>
-      <c r="H48" s="11">
-        <f t="shared" si="5"/>
+      <c r="H48" s="13" t="n">
+        <f aca="false">(D48-D47)/(B48-B47)</f>
         <v>106.25</v>
       </c>
-      <c r="I48" s="11">
-        <f t="shared" si="6"/>
+      <c r="I48" s="13" t="n">
+        <f aca="false">(F48-F47)/(B48-B47)</f>
         <v>63.5</v>
       </c>
-      <c r="J48" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J48" s="5" t="str">
+        <f aca="false">IF(AND(H48&gt;I48,H49&lt;=I49),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K48" s="14">
-        <f t="shared" si="8"/>
+      <c r="K48" s="16" t="n">
+        <f aca="false">(B48+B47)/2</f>
         <v>31250000</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B49" s="14">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="16" t="n">
         <v>35000000</v>
       </c>
-      <c r="C49" s="11">
-        <f t="shared" si="0"/>
+      <c r="C49" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B49</f>
         <v>290.5</v>
       </c>
-      <c r="D49" s="12">
-        <f t="shared" si="1"/>
+      <c r="D49" s="14" t="n">
+        <f aca="false">C49*B49</f>
         <v>10167500000</v>
       </c>
-      <c r="E49" s="12">
-        <f t="shared" si="2"/>
+      <c r="E49" s="14" t="n">
+        <f aca="false">g_a*B49+g_b*B49^2</f>
         <v>1260000000</v>
       </c>
-      <c r="F49" s="12">
-        <f t="shared" si="3"/>
+      <c r="F49" s="14" t="n">
+        <f aca="false">E49+g_FC</f>
         <v>1390000000</v>
       </c>
-      <c r="G49" s="12">
-        <f t="shared" si="4"/>
+      <c r="G49" s="14" t="n">
+        <f aca="false">D49-F49</f>
         <v>8777500000</v>
       </c>
-      <c r="H49" s="11">
-        <f t="shared" si="5"/>
+      <c r="H49" s="13" t="n">
+        <f aca="false">(D49-D48)/(B49-B48)</f>
         <v>72.75</v>
       </c>
-      <c r="I49" s="11">
-        <f t="shared" si="6"/>
+      <c r="I49" s="13" t="n">
+        <f aca="false">(F49-F48)/(B49-B48)</f>
         <v>68.5</v>
       </c>
-      <c r="J49" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J49" s="5" t="str">
+        <f aca="false">IF(AND(H49&gt;I49,H50&lt;=I50),"&lt;-- MR ~ MC","")</f>
         <v>&lt;-- MR ~ MC</v>
       </c>
-      <c r="K49" s="14">
-        <f t="shared" si="8"/>
+      <c r="K49" s="16" t="n">
+        <f aca="false">(B49+B48)/2</f>
         <v>33750000</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B50" s="14">
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="16" t="n">
         <v>37500000</v>
       </c>
-      <c r="C50" s="11">
-        <f t="shared" si="0"/>
+      <c r="C50" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B50</f>
         <v>273.75</v>
       </c>
-      <c r="D50" s="12">
-        <f t="shared" si="1"/>
+      <c r="D50" s="14" t="n">
+        <f aca="false">C50*B50</f>
         <v>10265625000</v>
       </c>
-      <c r="E50" s="12">
-        <f t="shared" si="2"/>
+      <c r="E50" s="14" t="n">
+        <f aca="false">g_a*B50+g_b*B50^2</f>
         <v>1443750000</v>
       </c>
-      <c r="F50" s="12">
-        <f t="shared" si="3"/>
+      <c r="F50" s="14" t="n">
+        <f aca="false">E50+g_FC</f>
         <v>1573750000</v>
       </c>
-      <c r="G50" s="12">
-        <f t="shared" si="4"/>
+      <c r="G50" s="14" t="n">
+        <f aca="false">D50-F50</f>
         <v>8691875000</v>
       </c>
-      <c r="H50" s="11">
-        <f t="shared" si="5"/>
+      <c r="H50" s="13" t="n">
+        <f aca="false">(D50-D49)/(B50-B49)</f>
         <v>39.25</v>
       </c>
-      <c r="I50" s="11">
-        <f t="shared" si="6"/>
+      <c r="I50" s="13" t="n">
+        <f aca="false">(F50-F49)/(B50-B49)</f>
         <v>73.5</v>
       </c>
-      <c r="J50" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J50" s="5" t="str">
+        <f aca="false">IF(AND(H50&gt;I50,H51&lt;=I51),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K50" s="14">
-        <f t="shared" si="8"/>
+      <c r="K50" s="16" t="n">
+        <f aca="false">(B50+B49)/2</f>
         <v>36250000</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B51" s="14">
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="16" t="n">
         <v>40000000</v>
       </c>
-      <c r="C51" s="11">
-        <f t="shared" si="0"/>
+      <c r="C51" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B51</f>
         <v>257</v>
       </c>
-      <c r="D51" s="12">
-        <f t="shared" si="1"/>
+      <c r="D51" s="14" t="n">
+        <f aca="false">C51*B51</f>
         <v>10280000000</v>
       </c>
-      <c r="E51" s="12">
-        <f t="shared" si="2"/>
+      <c r="E51" s="14" t="n">
+        <f aca="false">g_a*B51+g_b*B51^2</f>
         <v>1640000000</v>
       </c>
-      <c r="F51" s="12">
-        <f t="shared" si="3"/>
+      <c r="F51" s="14" t="n">
+        <f aca="false">E51+g_FC</f>
         <v>1770000000</v>
       </c>
-      <c r="G51" s="12">
-        <f t="shared" si="4"/>
+      <c r="G51" s="14" t="n">
+        <f aca="false">D51-F51</f>
         <v>8510000000</v>
       </c>
-      <c r="H51" s="11">
-        <f t="shared" si="5"/>
+      <c r="H51" s="13" t="n">
+        <f aca="false">(D51-D50)/(B51-B50)</f>
         <v>5.75</v>
       </c>
-      <c r="I51" s="11">
-        <f t="shared" si="6"/>
+      <c r="I51" s="13" t="n">
+        <f aca="false">(F51-F50)/(B51-B50)</f>
         <v>78.5</v>
       </c>
-      <c r="J51" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J51" s="5" t="str">
+        <f aca="false">IF(AND(H51&gt;I51,H52&lt;=I52),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K51" s="14">
-        <f t="shared" si="8"/>
+      <c r="K51" s="16" t="n">
+        <f aca="false">(B51+B50)/2</f>
         <v>38750000</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B52" s="14">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="16" t="n">
         <v>42500000</v>
       </c>
-      <c r="C52" s="11">
-        <f t="shared" si="0"/>
+      <c r="C52" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B52</f>
         <v>240.25</v>
       </c>
-      <c r="D52" s="12">
-        <f t="shared" si="1"/>
+      <c r="D52" s="14" t="n">
+        <f aca="false">C52*B52</f>
         <v>10210625000</v>
       </c>
-      <c r="E52" s="12">
-        <f t="shared" si="2"/>
+      <c r="E52" s="14" t="n">
+        <f aca="false">g_a*B52+g_b*B52^2</f>
         <v>1848750000</v>
       </c>
-      <c r="F52" s="12">
-        <f t="shared" si="3"/>
+      <c r="F52" s="14" t="n">
+        <f aca="false">E52+g_FC</f>
         <v>1978750000</v>
       </c>
-      <c r="G52" s="12">
-        <f t="shared" si="4"/>
+      <c r="G52" s="14" t="n">
+        <f aca="false">D52-F52</f>
         <v>8231875000</v>
       </c>
-      <c r="H52" s="11">
-        <f t="shared" si="5"/>
+      <c r="H52" s="13" t="n">
+        <f aca="false">(D52-D51)/(B52-B51)</f>
         <v>-27.75</v>
       </c>
-      <c r="I52" s="11">
-        <f t="shared" si="6"/>
+      <c r="I52" s="13" t="n">
+        <f aca="false">(F52-F51)/(B52-B51)</f>
         <v>83.5</v>
       </c>
-      <c r="J52" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J52" s="5" t="str">
+        <f aca="false">IF(AND(H52&gt;I52,H53&lt;=I53),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K52" s="14">
-        <f t="shared" si="8"/>
+      <c r="K52" s="16" t="n">
+        <f aca="false">(B52+B51)/2</f>
         <v>41250000</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B53" s="14">
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="16" t="n">
         <v>45000000</v>
       </c>
-      <c r="C53" s="11">
-        <f t="shared" si="0"/>
+      <c r="C53" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B53</f>
         <v>223.5</v>
       </c>
-      <c r="D53" s="12">
-        <f t="shared" si="1"/>
+      <c r="D53" s="14" t="n">
+        <f aca="false">C53*B53</f>
         <v>10057500000</v>
       </c>
-      <c r="E53" s="12">
-        <f t="shared" si="2"/>
+      <c r="E53" s="14" t="n">
+        <f aca="false">g_a*B53+g_b*B53^2</f>
         <v>2070000000</v>
       </c>
-      <c r="F53" s="12">
-        <f t="shared" si="3"/>
+      <c r="F53" s="14" t="n">
+        <f aca="false">E53+g_FC</f>
         <v>2200000000</v>
       </c>
-      <c r="G53" s="12">
-        <f t="shared" si="4"/>
+      <c r="G53" s="14" t="n">
+        <f aca="false">D53-F53</f>
         <v>7857500000</v>
       </c>
-      <c r="H53" s="11">
-        <f t="shared" si="5"/>
+      <c r="H53" s="13" t="n">
+        <f aca="false">(D53-D52)/(B53-B52)</f>
         <v>-61.25</v>
       </c>
-      <c r="I53" s="11">
-        <f t="shared" si="6"/>
+      <c r="I53" s="13" t="n">
+        <f aca="false">(F53-F52)/(B53-B52)</f>
         <v>88.5</v>
       </c>
-      <c r="J53" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J53" s="5" t="str">
+        <f aca="false">IF(AND(H53&gt;I53,H54&lt;=I54),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K53" s="14">
-        <f t="shared" si="8"/>
+      <c r="K53" s="16" t="n">
+        <f aca="false">(B53+B52)/2</f>
         <v>43750000</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B54" s="14">
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="16" t="n">
         <v>47500000</v>
       </c>
-      <c r="C54" s="11">
-        <f t="shared" si="0"/>
+      <c r="C54" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B54</f>
         <v>206.75</v>
       </c>
-      <c r="D54" s="12">
-        <f t="shared" si="1"/>
+      <c r="D54" s="14" t="n">
+        <f aca="false">C54*B54</f>
         <v>9820625000</v>
       </c>
-      <c r="E54" s="12">
-        <f t="shared" si="2"/>
+      <c r="E54" s="14" t="n">
+        <f aca="false">g_a*B54+g_b*B54^2</f>
         <v>2303750000</v>
       </c>
-      <c r="F54" s="12">
-        <f t="shared" si="3"/>
+      <c r="F54" s="14" t="n">
+        <f aca="false">E54+g_FC</f>
         <v>2433750000</v>
       </c>
-      <c r="G54" s="12">
-        <f t="shared" si="4"/>
+      <c r="G54" s="14" t="n">
+        <f aca="false">D54-F54</f>
         <v>7386875000</v>
       </c>
-      <c r="H54" s="11">
-        <f t="shared" si="5"/>
+      <c r="H54" s="13" t="n">
+        <f aca="false">(D54-D53)/(B54-B53)</f>
         <v>-94.75</v>
       </c>
-      <c r="I54" s="11">
-        <f t="shared" si="6"/>
+      <c r="I54" s="13" t="n">
+        <f aca="false">(F54-F53)/(B54-B53)</f>
         <v>93.5</v>
       </c>
-      <c r="J54" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J54" s="5" t="str">
+        <f aca="false">IF(AND(H54&gt;I54,H55&lt;=I55),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K54" s="14">
-        <f t="shared" si="8"/>
+      <c r="K54" s="16" t="n">
+        <f aca="false">(B54+B53)/2</f>
         <v>46250000</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B55" s="14">
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="16" t="n">
         <v>50000000</v>
       </c>
-      <c r="C55" s="11">
-        <f t="shared" si="0"/>
+      <c r="C55" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B55</f>
         <v>190</v>
       </c>
-      <c r="D55" s="12">
-        <f t="shared" si="1"/>
+      <c r="D55" s="14" t="n">
+        <f aca="false">C55*B55</f>
         <v>9500000000</v>
       </c>
-      <c r="E55" s="12">
-        <f t="shared" si="2"/>
+      <c r="E55" s="14" t="n">
+        <f aca="false">g_a*B55+g_b*B55^2</f>
         <v>2550000000</v>
       </c>
-      <c r="F55" s="12">
-        <f t="shared" si="3"/>
+      <c r="F55" s="14" t="n">
+        <f aca="false">E55+g_FC</f>
         <v>2680000000</v>
       </c>
-      <c r="G55" s="12">
-        <f t="shared" si="4"/>
+      <c r="G55" s="14" t="n">
+        <f aca="false">D55-F55</f>
         <v>6820000000</v>
       </c>
-      <c r="H55" s="11">
-        <f t="shared" si="5"/>
+      <c r="H55" s="13" t="n">
+        <f aca="false">(D55-D54)/(B55-B54)</f>
         <v>-128.25</v>
       </c>
-      <c r="I55" s="11">
-        <f t="shared" si="6"/>
+      <c r="I55" s="13" t="n">
+        <f aca="false">(F55-F54)/(B55-B54)</f>
         <v>98.5</v>
       </c>
-      <c r="J55" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J55" s="5" t="str">
+        <f aca="false">IF(AND(H55&gt;I55,H56&lt;=I56),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K55" s="14">
-        <f t="shared" si="8"/>
+      <c r="K55" s="16" t="n">
+        <f aca="false">(B55+B54)/2</f>
         <v>48750000</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B56" s="14">
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="16" t="n">
         <v>52500000</v>
       </c>
-      <c r="C56" s="11">
-        <f t="shared" si="0"/>
+      <c r="C56" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B56</f>
         <v>173.25</v>
       </c>
-      <c r="D56" s="12">
-        <f t="shared" si="1"/>
+      <c r="D56" s="14" t="n">
+        <f aca="false">C56*B56</f>
         <v>9095625000</v>
       </c>
-      <c r="E56" s="12">
-        <f t="shared" si="2"/>
+      <c r="E56" s="14" t="n">
+        <f aca="false">g_a*B56+g_b*B56^2</f>
         <v>2808750000</v>
       </c>
-      <c r="F56" s="12">
-        <f t="shared" si="3"/>
+      <c r="F56" s="14" t="n">
+        <f aca="false">E56+g_FC</f>
         <v>2938750000</v>
       </c>
-      <c r="G56" s="12">
-        <f t="shared" si="4"/>
+      <c r="G56" s="14" t="n">
+        <f aca="false">D56-F56</f>
         <v>6156875000</v>
       </c>
-      <c r="H56" s="11">
-        <f t="shared" si="5"/>
+      <c r="H56" s="13" t="n">
+        <f aca="false">(D56-D55)/(B56-B55)</f>
         <v>-161.75</v>
       </c>
-      <c r="I56" s="11">
-        <f t="shared" si="6"/>
+      <c r="I56" s="13" t="n">
+        <f aca="false">(F56-F55)/(B56-B55)</f>
         <v>103.5</v>
       </c>
-      <c r="J56" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J56" s="5" t="str">
+        <f aca="false">IF(AND(H56&gt;I56,H57&lt;=I57),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K56" s="14">
-        <f t="shared" si="8"/>
+      <c r="K56" s="16" t="n">
+        <f aca="false">(B56+B55)/2</f>
         <v>51250000</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B57" s="14">
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="16" t="n">
         <v>55000000</v>
       </c>
-      <c r="C57" s="11">
-        <f t="shared" si="0"/>
+      <c r="C57" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B57</f>
         <v>156.5</v>
       </c>
-      <c r="D57" s="12">
-        <f t="shared" si="1"/>
+      <c r="D57" s="14" t="n">
+        <f aca="false">C57*B57</f>
         <v>8607500000</v>
       </c>
-      <c r="E57" s="12">
-        <f t="shared" si="2"/>
+      <c r="E57" s="14" t="n">
+        <f aca="false">g_a*B57+g_b*B57^2</f>
         <v>3080000000</v>
       </c>
-      <c r="F57" s="12">
-        <f t="shared" si="3"/>
+      <c r="F57" s="14" t="n">
+        <f aca="false">E57+g_FC</f>
         <v>3210000000</v>
       </c>
-      <c r="G57" s="12">
-        <f t="shared" si="4"/>
+      <c r="G57" s="14" t="n">
+        <f aca="false">D57-F57</f>
         <v>5397500000</v>
       </c>
-      <c r="H57" s="11">
-        <f t="shared" si="5"/>
+      <c r="H57" s="13" t="n">
+        <f aca="false">(D57-D56)/(B57-B56)</f>
         <v>-195.25</v>
       </c>
-      <c r="I57" s="11">
-        <f t="shared" si="6"/>
+      <c r="I57" s="13" t="n">
+        <f aca="false">(F57-F56)/(B57-B56)</f>
         <v>108.5</v>
       </c>
-      <c r="J57" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J57" s="5" t="str">
+        <f aca="false">IF(AND(H57&gt;I57,H58&lt;=I58),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K57" s="14">
-        <f t="shared" si="8"/>
+      <c r="K57" s="16" t="n">
+        <f aca="false">(B57+B56)/2</f>
         <v>53750000</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B58" s="14">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="16" t="n">
         <v>57500000</v>
       </c>
-      <c r="C58" s="11">
-        <f t="shared" si="0"/>
+      <c r="C58" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B58</f>
         <v>139.75</v>
       </c>
-      <c r="D58" s="12">
-        <f t="shared" si="1"/>
+      <c r="D58" s="14" t="n">
+        <f aca="false">C58*B58</f>
         <v>8035625000</v>
       </c>
-      <c r="E58" s="12">
-        <f t="shared" si="2"/>
+      <c r="E58" s="14" t="n">
+        <f aca="false">g_a*B58+g_b*B58^2</f>
         <v>3363750000</v>
       </c>
-      <c r="F58" s="12">
-        <f t="shared" si="3"/>
+      <c r="F58" s="14" t="n">
+        <f aca="false">E58+g_FC</f>
         <v>3493750000</v>
       </c>
-      <c r="G58" s="12">
-        <f t="shared" si="4"/>
+      <c r="G58" s="14" t="n">
+        <f aca="false">D58-F58</f>
         <v>4541875000</v>
       </c>
-      <c r="H58" s="11">
-        <f t="shared" si="5"/>
+      <c r="H58" s="13" t="n">
+        <f aca="false">(D58-D57)/(B58-B57)</f>
         <v>-228.75</v>
       </c>
-      <c r="I58" s="11">
-        <f t="shared" si="6"/>
+      <c r="I58" s="13" t="n">
+        <f aca="false">(F58-F57)/(B58-B57)</f>
         <v>113.5</v>
       </c>
-      <c r="J58" s="6" t="str">
-        <f t="shared" si="7"/>
+      <c r="J58" s="5" t="str">
+        <f aca="false">IF(AND(H58&gt;I58,H59&lt;=I59),"&lt;-- MR ~ MC","")</f>
         <v/>
       </c>
-      <c r="K58" s="14">
-        <f t="shared" si="8"/>
+      <c r="K58" s="16" t="n">
+        <f aca="false">(B58+B57)/2</f>
         <v>56250000</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B59" s="14">
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="16" t="n">
         <v>60000000</v>
       </c>
-      <c r="C59" s="11">
-        <f t="shared" si="0"/>
+      <c r="C59" s="13" t="n">
+        <f aca="false">g_Di+g_Ds*B59</f>
         <v>123</v>
       </c>
-      <c r="D59" s="12">
-        <f t="shared" si="1"/>
+      <c r="D59" s="14" t="n">
+        <f aca="false">C59*B59</f>
         <v>7380000000</v>
       </c>
-      <c r="E59" s="12">
-        <f t="shared" si="2"/>
+      <c r="E59" s="14" t="n">
+        <f aca="false">g_a*B59+g_b*B59^2</f>
         <v>3660000000</v>
       </c>
-      <c r="F59" s="12">
-        <f t="shared" si="3"/>
+      <c r="F59" s="14" t="n">
+        <f aca="false">E59+g_FC</f>
         <v>3790000000</v>
       </c>
-      <c r="G59" s="12">
-        <f t="shared" si="4"/>
+      <c r="G59" s="14" t="n">
+        <f aca="false">D59-F59</f>
         <v>3590000000</v>
       </c>
-      <c r="H59" s="11">
-        <f t="shared" si="5"/>
+      <c r="H59" s="13" t="n">
+        <f aca="false">(D59-D58)/(B59-B58)</f>
         <v>-262.25</v>
       </c>
-      <c r="I59" s="11">
-        <f t="shared" si="6"/>
+      <c r="I59" s="13" t="n">
+        <f aca="false">(F59-F58)/(B59-B58)</f>
         <v>118.5</v>
       </c>
-      <c r="K59" s="14">
-        <f t="shared" si="8"/>
+      <c r="K59" s="16" t="n">
+        <f aca="false">(B59+B58)/2</f>
         <v>58750000</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>